--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_13.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,3335 +469,6285 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:58.457</t>
+          <t>2026-05-29 09:40:12.059</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421920614</v>
+        <v>1780022410619</v>
       </c>
       <c r="C2" t="n">
-        <v>87185</v>
+        <v>83545</v>
       </c>
       <c r="D2" t="n">
-        <v>11248.95</v>
+        <v>-164.05</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G2" t="n">
-        <v>37.38</v>
+        <v>279.59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="L2" t="n">
+        <v>106</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.027</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:58.961</t>
+          <t>2026-05-29 09:40:12.314</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421920816</v>
+        <v>1780022410838</v>
       </c>
       <c r="C3" t="n">
-        <v>86895</v>
+        <v>84127</v>
       </c>
       <c r="D3" t="n">
-        <v>10396.51</v>
+        <v>426.15</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G3" t="n">
-        <v>37.38</v>
+        <v>279.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1474</v>
+      </c>
+      <c r="L3" t="n">
+        <v>122</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:58.962</t>
+          <t>2026-05-29 09:40:12.316</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421921017</v>
+        <v>1780022411038</v>
       </c>
       <c r="C4" t="n">
-        <v>86912</v>
+        <v>84865</v>
       </c>
       <c r="D4" t="n">
-        <v>9893.68</v>
+        <v>1142.84</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G4" t="n">
-        <v>37.38</v>
+        <v>279.59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L4" t="n">
+        <v>106</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:59.292</t>
+          <t>2026-05-29 09:40:12.317</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421921219</v>
+        <v>1780022411238</v>
       </c>
       <c r="C5" t="n">
-        <v>87061</v>
+        <v>84449</v>
       </c>
       <c r="D5" t="n">
-        <v>9548</v>
+        <v>669.7</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G5" t="n">
-        <v>37.38</v>
+        <v>279.59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L5" t="n">
+        <v>107</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:59.293</t>
+          <t>2026-05-29 09:40:12.829</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421921420</v>
+        <v>1780022411439</v>
       </c>
       <c r="C6" t="n">
-        <v>87295</v>
+        <v>85082</v>
       </c>
       <c r="D6" t="n">
-        <v>9304.6</v>
+        <v>1269.22</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G6" t="n">
-        <v>30.32</v>
+        <v>279.59</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1387</v>
+      </c>
+      <c r="L6" t="n">
+        <v>113</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.062</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:59.679</t>
+          <t>2026-05-29 09:40:12.830</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421921621</v>
+        <v>1780022411638</v>
       </c>
       <c r="C7" t="n">
-        <v>87066</v>
+        <v>84940</v>
       </c>
       <c r="D7" t="n">
-        <v>8610.370000000001</v>
+        <v>1063.75</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G7" t="n">
-        <v>30.32</v>
+        <v>279.59</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L7" t="n">
+        <v>117</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:51:59.679</t>
+          <t>2026-05-29 09:40:12.833</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421921823</v>
+        <v>1780022411838</v>
       </c>
       <c r="C8" t="n">
-        <v>86997</v>
+        <v>86254</v>
       </c>
       <c r="D8" t="n">
-        <v>8110.85</v>
+        <v>2324.57</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G8" t="n">
-        <v>30.32</v>
+        <v>279.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K8" t="n">
+        <v>993</v>
+      </c>
+      <c r="L8" t="n">
+        <v>108</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.747</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:00.103</t>
+          <t>2026-05-29 09:40:13.276</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421922024</v>
+        <v>1780022412038</v>
       </c>
       <c r="C9" t="n">
-        <v>87120</v>
+        <v>87558</v>
       </c>
       <c r="D9" t="n">
-        <v>7828.31</v>
+        <v>3512.34</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G9" t="n">
-        <v>30.32</v>
+        <v>279.59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1238</v>
+      </c>
+      <c r="L9" t="n">
+        <v>123</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:00.117</t>
+          <t>2026-05-29 09:40:13.278</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421922226</v>
+        <v>1780022412238</v>
       </c>
       <c r="C10" t="n">
-        <v>87292</v>
+        <v>88989</v>
       </c>
       <c r="D10" t="n">
-        <v>7608.89</v>
+        <v>4767.72</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>866</v>
+        <v>1379</v>
       </c>
       <c r="G10" t="n">
-        <v>40.54</v>
+        <v>279.59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1039</v>
+      </c>
+      <c r="L10" t="n">
+        <v>108</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:00.494</t>
+          <t>2026-05-29 09:40:13.877</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421922427</v>
+        <v>1780022412457</v>
       </c>
       <c r="C11" t="n">
-        <v>86752</v>
+        <v>88804</v>
       </c>
       <c r="D11" t="n">
-        <v>6688.45</v>
+        <v>4344.34</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>866</v>
+        <v>1379</v>
       </c>
       <c r="G11" t="n">
-        <v>40.54</v>
+        <v>279.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1419</v>
+      </c>
+      <c r="L11" t="n">
+        <v>120</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:00.525</t>
+          <t>2026-05-29 09:40:13.879</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421922628</v>
+        <v>1780022412657</v>
       </c>
       <c r="C12" t="n">
-        <v>87016</v>
+        <v>86941</v>
       </c>
       <c r="D12" t="n">
-        <v>6618.02</v>
+        <v>2264.12</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>866</v>
+        <v>1379</v>
       </c>
       <c r="G12" t="n">
-        <v>40.54</v>
+        <v>279.59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L12" t="n">
+        <v>109</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.317</t>
+          <t>2026-05-29 09:40:14.100</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421922830</v>
+        <v>1780022412857</v>
       </c>
       <c r="C13" t="n">
-        <v>87592</v>
+        <v>87640</v>
       </c>
       <c r="D13" t="n">
-        <v>6863.12</v>
+        <v>2849.91</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>866</v>
+        <v>1379</v>
       </c>
       <c r="G13" t="n">
-        <v>40.54</v>
+        <v>279.59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L13" t="n">
+        <v>126</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.325</t>
+          <t>2026-05-29 09:40:14.109</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421923031</v>
+        <v>1780022413057</v>
       </c>
       <c r="C14" t="n">
-        <v>87874</v>
+        <v>90053</v>
       </c>
       <c r="D14" t="n">
-        <v>6801.97</v>
+        <v>5120.42</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G14" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L14" t="n">
+        <v>108</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.327</t>
+          <t>2026-05-29 09:40:14.153</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421923233</v>
+        <v>1780022413257</v>
       </c>
       <c r="C15" t="n">
-        <v>86653</v>
+        <v>89063</v>
       </c>
       <c r="D15" t="n">
-        <v>5240.87</v>
+        <v>3874.4</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G15" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K15" t="n">
+        <v>895</v>
+      </c>
+      <c r="L15" t="n">
+        <v>107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.356</t>
+          <t>2026-05-29 09:40:16.179</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421923434</v>
+        <v>1780022413457</v>
       </c>
       <c r="C16" t="n">
-        <v>86630</v>
+        <v>88930</v>
       </c>
       <c r="D16" t="n">
-        <v>4955.83</v>
+        <v>3547.68</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G16" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L16" t="n">
+        <v>120</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.729</t>
+          <t>2026-05-29 09:40:16.223</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421923635</v>
+        <v>1780022413657</v>
       </c>
       <c r="C17" t="n">
-        <v>86890</v>
+        <v>88243</v>
       </c>
       <c r="D17" t="n">
-        <v>4968.03</v>
+        <v>2683.29</v>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G17" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2565</v>
+      </c>
+      <c r="L17" t="n">
+        <v>120</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:01.735</t>
+          <t>2026-05-29 09:40:16.229</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421923837</v>
+        <v>1780022413857</v>
       </c>
       <c r="C18" t="n">
-        <v>87504</v>
+        <v>88246</v>
       </c>
       <c r="D18" t="n">
-        <v>5333.63</v>
+        <v>2552.13</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G18" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2371</v>
+      </c>
+      <c r="L18" t="n">
+        <v>107</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.145</t>
+          <t>2026-05-29 09:40:16.262</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421924038</v>
+        <v>1780022414057</v>
       </c>
       <c r="C19" t="n">
-        <v>86751</v>
+        <v>88093</v>
       </c>
       <c r="D19" t="n">
-        <v>4313.95</v>
+        <v>2271.52</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G19" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2204</v>
+      </c>
+      <c r="L19" t="n">
+        <v>105</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.212</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.146</t>
+          <t>2026-05-29 09:40:16.264</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421924240</v>
+        <v>1780022414257</v>
       </c>
       <c r="C20" t="n">
-        <v>86778</v>
+        <v>87610</v>
       </c>
       <c r="D20" t="n">
-        <v>4125.25</v>
+        <v>1674.95</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G20" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2006</v>
+      </c>
+      <c r="L20" t="n">
+        <v>107</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.877</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.941</t>
+          <t>2026-05-29 09:40:16.265</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421924441</v>
+        <v>1780022414476</v>
       </c>
       <c r="C21" t="n">
-        <v>86815</v>
+        <v>88204</v>
       </c>
       <c r="D21" t="n">
-        <v>3955.99</v>
+        <v>2185.2</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G21" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1788</v>
+      </c>
+      <c r="L21" t="n">
+        <v>106</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.012</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.942</t>
+          <t>2026-05-29 09:40:16.267</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421924642</v>
+        <v>1780022414676</v>
       </c>
       <c r="C22" t="n">
-        <v>86776</v>
+        <v>87700</v>
       </c>
       <c r="D22" t="n">
-        <v>3719.19</v>
+        <v>1571.94</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G22" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1590</v>
+      </c>
+      <c r="L22" t="n">
+        <v>120</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.942</t>
+          <t>2026-05-29 09:40:16.268</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421924844</v>
+        <v>1780022414876</v>
       </c>
       <c r="C23" t="n">
-        <v>86190</v>
+        <v>87013</v>
       </c>
       <c r="D23" t="n">
-        <v>2947.23</v>
+        <v>806.34</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G23" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1391</v>
+      </c>
+      <c r="L23" t="n">
+        <v>108</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.498</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:02.943</t>
+          <t>2026-05-29 09:40:16.269</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421925045</v>
+        <v>1780022415076</v>
       </c>
       <c r="C24" t="n">
-        <v>86347</v>
+        <v>86450</v>
       </c>
       <c r="D24" t="n">
-        <v>2956.87</v>
+        <v>203.02</v>
       </c>
       <c r="E24" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G24" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1192</v>
+      </c>
+      <c r="L24" t="n">
+        <v>109</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.656</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:03.349</t>
+          <t>2026-05-29 09:40:16.328</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421925247</v>
+        <v>1780022415276</v>
       </c>
       <c r="C25" t="n">
-        <v>86551</v>
+        <v>86491</v>
       </c>
       <c r="D25" t="n">
-        <v>3013.03</v>
+        <v>233.87</v>
       </c>
       <c r="E25" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>665</v>
+        <v>1379</v>
       </c>
       <c r="G25" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L25" t="n">
+        <v>118</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:03.350</t>
+          <t>2026-05-29 09:40:16.388</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421925448</v>
+        <v>1780022415476</v>
       </c>
       <c r="C26" t="n">
-        <v>86061</v>
+        <v>87599</v>
       </c>
       <c r="D26" t="n">
-        <v>2372.38</v>
+        <v>1330.18</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>2497</v>
+        <v>1379</v>
       </c>
       <c r="G26" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K26" t="n">
+        <v>911</v>
+      </c>
+      <c r="L26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.062</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:03.763</t>
+          <t>2026-05-29 09:40:16.808</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421925649</v>
+        <v>1780022415676</v>
       </c>
       <c r="C27" t="n">
-        <v>86181</v>
+        <v>87153</v>
       </c>
       <c r="D27" t="n">
-        <v>2373.76</v>
+        <v>817.67</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>2497</v>
+        <v>1379</v>
       </c>
       <c r="G27" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1131</v>
+      </c>
+      <c r="L27" t="n">
+        <v>126</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:03.763</t>
+          <t>2026-05-29 09:40:16.809</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421925851</v>
+        <v>1780022415876</v>
       </c>
       <c r="C28" t="n">
-        <v>86334</v>
+        <v>87044</v>
       </c>
       <c r="D28" t="n">
-        <v>2408.07</v>
+        <v>667.79</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>2497</v>
+        <v>1379</v>
       </c>
       <c r="G28" t="n">
-        <v>53.18</v>
+        <v>279.59</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K28" t="n">
+        <v>932</v>
+      </c>
+      <c r="L28" t="n">
+        <v>121</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.011</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.424</t>
+          <t>2026-05-29 09:40:17.866</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421926052</v>
+        <v>1780022416076</v>
       </c>
       <c r="C29" t="n">
-        <v>86616</v>
+        <v>87727</v>
       </c>
       <c r="D29" t="n">
-        <v>2569.67</v>
+        <v>1317.4</v>
       </c>
       <c r="E29" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>645</v>
+        <v>1379</v>
       </c>
       <c r="G29" t="n">
-        <v>64.98</v>
+        <v>279.59</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1788</v>
+      </c>
+      <c r="L29" t="n">
+        <v>121</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.368</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.424</t>
+          <t>2026-05-29 09:40:17.867</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421926254</v>
+        <v>1780022416276</v>
       </c>
       <c r="C30" t="n">
-        <v>85934</v>
+        <v>88490</v>
       </c>
       <c r="D30" t="n">
-        <v>1759.18</v>
+        <v>2014.53</v>
       </c>
       <c r="E30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" t="n">
-        <v>645</v>
+        <v>1379</v>
       </c>
       <c r="G30" t="n">
-        <v>64.98</v>
+        <v>279.59</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1591</v>
+      </c>
+      <c r="L30" t="n">
+        <v>119</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.857</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.425</t>
+          <t>2026-05-29 09:40:17.869</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421926455</v>
+        <v>1780022416495</v>
       </c>
       <c r="C31" t="n">
-        <v>86305</v>
+        <v>87072</v>
       </c>
       <c r="D31" t="n">
-        <v>2042.22</v>
+        <v>495.8</v>
       </c>
       <c r="E31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F31" t="n">
-        <v>645</v>
+        <v>1379</v>
       </c>
       <c r="G31" t="n">
-        <v>64.98</v>
+        <v>279.59</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1373</v>
+      </c>
+      <c r="L31" t="n">
+        <v>107</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.425</t>
+          <t>2026-05-29 09:40:17.870</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421926656</v>
+        <v>1780022416695</v>
       </c>
       <c r="C32" t="n">
-        <v>86570</v>
+        <v>87334</v>
       </c>
       <c r="D32" t="n">
-        <v>2205.11</v>
+        <v>733.01</v>
       </c>
       <c r="E32" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F32" t="n">
-        <v>664</v>
+        <v>1379</v>
       </c>
       <c r="G32" t="n">
-        <v>69.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L32" t="n">
+        <v>111</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.586</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.893</t>
+          <t>2026-05-29 09:40:19.727</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421926858</v>
+        <v>1780022416895</v>
       </c>
       <c r="C33" t="n">
-        <v>86814</v>
+        <v>87117</v>
       </c>
       <c r="D33" t="n">
-        <v>2338.86</v>
+        <v>479.36</v>
       </c>
       <c r="E33" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F33" t="n">
-        <v>664</v>
+        <v>1379</v>
       </c>
       <c r="G33" t="n">
-        <v>69.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2831</v>
+      </c>
+      <c r="L33" t="n">
+        <v>110</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.585</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:04.893</t>
+          <t>2026-05-29 09:40:19.770</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421927059</v>
+        <v>1780022417095</v>
       </c>
       <c r="C34" t="n">
-        <v>86195</v>
+        <v>86966</v>
       </c>
       <c r="D34" t="n">
-        <v>1602.91</v>
+        <v>304.39</v>
       </c>
       <c r="E34" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F34" t="n">
-        <v>664</v>
+        <v>1379</v>
       </c>
       <c r="G34" t="n">
-        <v>69.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J34" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2674</v>
+      </c>
+      <c r="L34" t="n">
+        <v>122</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:05.218</t>
+          <t>2026-05-29 09:40:19.772</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421927261</v>
+        <v>1780022417295</v>
       </c>
       <c r="C35" t="n">
-        <v>86389</v>
+        <v>86619</v>
       </c>
       <c r="D35" t="n">
-        <v>1716.77</v>
+        <v>-57.83</v>
       </c>
       <c r="E35" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F35" t="n">
-        <v>664</v>
+        <v>1379</v>
       </c>
       <c r="G35" t="n">
-        <v>69.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J35" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2475</v>
+      </c>
+      <c r="L35" t="n">
+        <v>114</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.362</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:05.218</t>
+          <t>2026-05-29 09:40:19.774</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421927462</v>
+        <v>1780022417495</v>
       </c>
       <c r="C36" t="n">
-        <v>86588</v>
+        <v>86496</v>
       </c>
       <c r="D36" t="n">
-        <v>1829.93</v>
+        <v>-177.94</v>
       </c>
       <c r="E36" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F36" t="n">
-        <v>664</v>
+        <v>1379</v>
       </c>
       <c r="G36" t="n">
-        <v>69.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J36" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2277</v>
+      </c>
+      <c r="L36" t="n">
+        <v>112</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.503</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:05.446</t>
+          <t>2026-05-29 09:40:19.775</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421927664</v>
+        <v>1780022418334</v>
       </c>
       <c r="C37" t="n">
-        <v>86693</v>
+        <v>88124</v>
       </c>
       <c r="D37" t="n">
-        <v>1843.43</v>
+        <v>1458.96</v>
       </c>
       <c r="E37" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F37" t="n">
-        <v>867</v>
+        <v>1379</v>
       </c>
       <c r="G37" t="n">
-        <v>78.53</v>
+        <v>279.59</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1440</v>
+      </c>
+      <c r="L37" t="n">
+        <v>109</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:05.812</t>
+          <t>2026-05-29 09:40:19.776</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421927865</v>
+        <v>1780022418534</v>
       </c>
       <c r="C38" t="n">
-        <v>86211</v>
+        <v>88419</v>
       </c>
       <c r="D38" t="n">
-        <v>1269.26</v>
+        <v>1681.01</v>
       </c>
       <c r="E38" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F38" t="n">
-        <v>867</v>
+        <v>1379</v>
       </c>
       <c r="G38" t="n">
-        <v>78.53</v>
+        <v>279.59</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L38" t="n">
+        <v>122</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:05.812</t>
+          <t>2026-05-29 09:40:19.779</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421928066</v>
+        <v>1780022418734</v>
       </c>
       <c r="C39" t="n">
-        <v>86459</v>
+        <v>87496</v>
       </c>
       <c r="D39" t="n">
-        <v>1453.8</v>
+        <v>673.96</v>
       </c>
       <c r="E39" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F39" t="n">
-        <v>867</v>
+        <v>1379</v>
       </c>
       <c r="G39" t="n">
-        <v>78.53</v>
+        <v>279.59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1044</v>
+      </c>
+      <c r="L39" t="n">
+        <v>109</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:06.328</t>
+          <t>2026-05-29 09:40:20.336</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421928268</v>
+        <v>1780022418934</v>
       </c>
       <c r="C40" t="n">
-        <v>86674</v>
+        <v>86601</v>
       </c>
       <c r="D40" t="n">
-        <v>1596.11</v>
+        <v>-254.74</v>
       </c>
       <c r="E40" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F40" t="n">
-        <v>705</v>
+        <v>1379</v>
       </c>
       <c r="G40" t="n">
-        <v>79.98999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L40" t="n">
+        <v>115</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.189</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:06.344</t>
+          <t>2026-05-29 09:40:20.337</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421928469</v>
+        <v>1780022419134</v>
       </c>
       <c r="C41" t="n">
-        <v>86294</v>
+        <v>85327</v>
       </c>
       <c r="D41" t="n">
-        <v>1136.3</v>
+        <v>-1516</v>
       </c>
       <c r="E41" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F41" t="n">
-        <v>705</v>
+        <v>1379</v>
       </c>
       <c r="G41" t="n">
-        <v>79.98999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L41" t="n">
+        <v>122</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.785</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:06.642</t>
+          <t>2026-05-29 09:40:20.638</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421928671</v>
+        <v>1780022419335</v>
       </c>
       <c r="C42" t="n">
-        <v>86287</v>
+        <v>85643</v>
       </c>
       <c r="D42" t="n">
-        <v>1072.49</v>
+        <v>-1124.2</v>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F42" t="n">
-        <v>705</v>
+        <v>1379</v>
       </c>
       <c r="G42" t="n">
-        <v>79.98999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1301</v>
+      </c>
+      <c r="L42" t="n">
+        <v>106</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.251</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:06.670</t>
+          <t>2026-05-29 09:40:20.638</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421928872</v>
+        <v>1780022419534</v>
       </c>
       <c r="C43" t="n">
-        <v>86540</v>
+        <v>86244</v>
       </c>
       <c r="D43" t="n">
-        <v>1271.86</v>
+        <v>-466.99</v>
       </c>
       <c r="E43" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F43" t="n">
-        <v>705</v>
+        <v>1379</v>
       </c>
       <c r="G43" t="n">
-        <v>79.98999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1104</v>
+      </c>
+      <c r="L43" t="n">
+        <v>109</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.543</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:07.071</t>
+          <t>2026-05-29 09:40:20.640</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421929073</v>
+        <v>1780022419734</v>
       </c>
       <c r="C44" t="n">
-        <v>86849</v>
+        <v>86333</v>
       </c>
       <c r="D44" t="n">
-        <v>1517.27</v>
+        <v>-354.64</v>
       </c>
       <c r="E44" t="n">
         <v>81</v>
       </c>
       <c r="F44" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G44" t="n">
-        <v>78.94</v>
+        <v>279.59</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K44" t="n">
+        <v>904</v>
+      </c>
+      <c r="L44" t="n">
+        <v>107</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.117</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:07.071</t>
+          <t>2026-05-29 09:40:20.640</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421929275</v>
+        <v>1780022419935</v>
       </c>
       <c r="C45" t="n">
-        <v>86313</v>
+        <v>86457</v>
       </c>
       <c r="D45" t="n">
-        <v>905.41</v>
+        <v>-212.91</v>
       </c>
       <c r="E45" t="n">
         <v>81</v>
       </c>
       <c r="F45" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G45" t="n">
-        <v>78.94</v>
+        <v>279.59</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K45" t="n">
+        <v>705</v>
+      </c>
+      <c r="L45" t="n">
+        <v>106</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:07.480</t>
+          <t>2026-05-29 09:40:21.709</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421929476</v>
+        <v>1780022420153</v>
       </c>
       <c r="C46" t="n">
-        <v>86567</v>
+        <v>86377</v>
       </c>
       <c r="D46" t="n">
-        <v>1114.14</v>
+        <v>-282.26</v>
       </c>
       <c r="E46" t="n">
         <v>81</v>
       </c>
       <c r="F46" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G46" t="n">
-        <v>78.94</v>
+        <v>279.59</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L46" t="n">
+        <v>110</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:07.481</t>
+          <t>2026-05-29 09:40:22.099</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421929678</v>
+        <v>1780022420354</v>
       </c>
       <c r="C47" t="n">
-        <v>86751</v>
+        <v>85666</v>
       </c>
       <c r="D47" t="n">
-        <v>1242.43</v>
+        <v>-979.15</v>
       </c>
       <c r="E47" t="n">
         <v>81</v>
       </c>
       <c r="F47" t="n">
-        <v>745</v>
+        <v>1379</v>
       </c>
       <c r="G47" t="n">
-        <v>78.94</v>
+        <v>279.59</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="J47" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1744</v>
+      </c>
+      <c r="L47" t="n">
+        <v>160</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.859</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.090</t>
+          <t>2026-05-29 09:40:22.111</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421929879</v>
+        <v>1780022420553</v>
       </c>
       <c r="C48" t="n">
-        <v>87005</v>
+        <v>85426</v>
       </c>
       <c r="D48" t="n">
-        <v>1434.31</v>
+        <v>-1170.19</v>
       </c>
       <c r="E48" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F48" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G48" t="n">
-        <v>78.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1557</v>
+      </c>
+      <c r="L48" t="n">
+        <v>110</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.729</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.091</t>
+          <t>2026-05-29 09:40:22.112</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421930081</v>
+        <v>1780022420753</v>
       </c>
       <c r="C49" t="n">
-        <v>86346</v>
+        <v>84945</v>
       </c>
       <c r="D49" t="n">
-        <v>703.59</v>
+        <v>-1592.68</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F49" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G49" t="n">
-        <v>78.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L49" t="n">
+        <v>112</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.064</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.338</t>
+          <t>2026-05-29 09:40:22.120</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421930282</v>
+        <v>1780022420953</v>
       </c>
       <c r="C50" t="n">
-        <v>86558</v>
+        <v>83856</v>
       </c>
       <c r="D50" t="n">
-        <v>880.41</v>
+        <v>-2602.05</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F50" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G50" t="n">
-        <v>78.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L50" t="n">
+        <v>110</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.729</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.339</t>
+          <t>2026-05-29 09:40:22.591</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421930483</v>
+        <v>1780022421153</v>
       </c>
       <c r="C51" t="n">
-        <v>86845</v>
+        <v>83072</v>
       </c>
       <c r="D51" t="n">
-        <v>1123.39</v>
+        <v>-3255.95</v>
       </c>
       <c r="E51" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F51" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G51" t="n">
-        <v>78.06999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L51" t="n">
+        <v>122</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.695</t>
+          <t>2026-05-29 09:40:22.692</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421930685</v>
+        <v>1780022421353</v>
       </c>
       <c r="C52" t="n">
-        <v>86936</v>
+        <v>83692</v>
       </c>
       <c r="D52" t="n">
-        <v>1158.22</v>
+        <v>-2473.15</v>
       </c>
       <c r="E52" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F52" t="n">
-        <v>806</v>
+        <v>1379</v>
       </c>
       <c r="G52" t="n">
-        <v>80.56999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1338</v>
+      </c>
+      <c r="L52" t="n">
+        <v>146</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:08.696</t>
+          <t>2026-05-29 09:40:22.722</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421930886</v>
+        <v>1780022421553</v>
       </c>
       <c r="C53" t="n">
-        <v>86437</v>
+        <v>85491</v>
       </c>
       <c r="D53" t="n">
-        <v>601.3099999999999</v>
+        <v>-550.49</v>
       </c>
       <c r="E53" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F53" t="n">
-        <v>806</v>
+        <v>1379</v>
       </c>
       <c r="G53" t="n">
-        <v>80.56999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L53" t="n">
+        <v>121</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.801</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:09.141</t>
+          <t>2026-05-29 09:40:22.737</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421931088</v>
+        <v>1780022421753</v>
       </c>
       <c r="C54" t="n">
-        <v>86626</v>
+        <v>86222</v>
       </c>
       <c r="D54" t="n">
-        <v>760.25</v>
+        <v>208.03</v>
       </c>
       <c r="E54" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F54" t="n">
-        <v>806</v>
+        <v>1379</v>
       </c>
       <c r="G54" t="n">
-        <v>80.56999999999999</v>
+        <v>279.59</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K54" t="n">
+        <v>983</v>
+      </c>
+      <c r="L54" t="n">
+        <v>108</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:09.142</t>
+          <t>2026-05-29 09:40:23.857</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421931289</v>
+        <v>1780022421972</v>
       </c>
       <c r="C55" t="n">
-        <v>86959</v>
+        <v>86388</v>
       </c>
       <c r="D55" t="n">
-        <v>1055.23</v>
+        <v>363.63</v>
       </c>
       <c r="E55" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F55" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G55" t="n">
-        <v>80.7</v>
+        <v>279.59</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1884</v>
+      </c>
+      <c r="L55" t="n">
+        <v>110</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.322</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:09.525</t>
+          <t>2026-05-29 09:40:23.979</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421931490</v>
+        <v>1780022422172</v>
       </c>
       <c r="C56" t="n">
-        <v>86453</v>
+        <v>87261</v>
       </c>
       <c r="D56" t="n">
-        <v>496.47</v>
+        <v>1218.45</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F56" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G56" t="n">
-        <v>80.7</v>
+        <v>279.59</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1805</v>
+      </c>
+      <c r="L56" t="n">
+        <v>107</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.024</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:09.540</t>
+          <t>2026-05-29 09:40:24.319</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421931692</v>
+        <v>1780022422372</v>
       </c>
       <c r="C57" t="n">
-        <v>86442</v>
+        <v>87629</v>
       </c>
       <c r="D57" t="n">
-        <v>460.65</v>
+        <v>1525.53</v>
       </c>
       <c r="E57" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F57" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G57" t="n">
-        <v>80.7</v>
+        <v>279.59</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1945</v>
+      </c>
+      <c r="L57" t="n">
+        <v>115</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.267</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.117</t>
+          <t>2026-05-29 09:40:24.320</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421931893</v>
+        <v>1780022422572</v>
       </c>
       <c r="C58" t="n">
-        <v>86698</v>
+        <v>86955</v>
       </c>
       <c r="D58" t="n">
-        <v>693.62</v>
+        <v>775.25</v>
       </c>
       <c r="E58" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F58" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G58" t="n">
-        <v>80.7</v>
+        <v>279.59</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1747</v>
+      </c>
+      <c r="L58" t="n">
+        <v>111</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.246</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.120</t>
+          <t>2026-05-29 09:40:24.322</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421932095</v>
+        <v>1780022422772</v>
       </c>
       <c r="C59" t="n">
-        <v>86927</v>
+        <v>86495</v>
       </c>
       <c r="D59" t="n">
-        <v>887.9400000000001</v>
+        <v>276.49</v>
       </c>
       <c r="E59" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F59" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G59" t="n">
-        <v>69.45</v>
+        <v>279.59</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1549</v>
+      </c>
+      <c r="L59" t="n">
+        <v>109</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.301</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.122</t>
+          <t>2026-05-29 09:40:24.323</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421932296</v>
+        <v>1780022422972</v>
       </c>
       <c r="C60" t="n">
-        <v>86090</v>
+        <v>86203</v>
       </c>
       <c r="D60" t="n">
-        <v>6.54</v>
+        <v>-29.34</v>
       </c>
       <c r="E60" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F60" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G60" t="n">
-        <v>69.45</v>
+        <v>279.59</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L60" t="n">
+        <v>106</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.918</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.538</t>
+          <t>2026-05-29 09:40:25.372</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421932497</v>
+        <v>1780022423172</v>
       </c>
       <c r="C61" t="n">
-        <v>86416</v>
+        <v>86145</v>
       </c>
       <c r="D61" t="n">
-        <v>332.21</v>
+        <v>-85.87</v>
       </c>
       <c r="E61" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F61" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G61" t="n">
-        <v>69.45</v>
+        <v>279.59</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2198</v>
+      </c>
+      <c r="L61" t="n">
+        <v>107</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.540</t>
+          <t>2026-05-29 09:40:25.383</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421932699</v>
+        <v>1780022423372</v>
       </c>
       <c r="C62" t="n">
-        <v>86681</v>
+        <v>85870</v>
       </c>
       <c r="D62" t="n">
-        <v>580.6</v>
+        <v>-356.58</v>
       </c>
       <c r="E62" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F62" t="n">
-        <v>765</v>
+        <v>1379</v>
       </c>
       <c r="G62" t="n">
-        <v>69.45</v>
+        <v>279.59</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J62" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L62" t="n">
+        <v>111</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.489</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.932</t>
+          <t>2026-05-29 09:40:25.394</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421932900</v>
+        <v>1780022423591</v>
       </c>
       <c r="C63" t="n">
-        <v>86759</v>
+        <v>85641</v>
       </c>
       <c r="D63" t="n">
-        <v>629.5700000000001</v>
+        <v>-567.75</v>
       </c>
       <c r="E63" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F63" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G63" t="n">
-        <v>65.17</v>
+        <v>279.59</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1802</v>
+      </c>
+      <c r="L63" t="n">
+        <v>117</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.708</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:10.933</t>
+          <t>2026-05-29 09:40:25.424</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421933102</v>
+        <v>1780022423791</v>
       </c>
       <c r="C64" t="n">
-        <v>86357</v>
+        <v>86007</v>
       </c>
       <c r="D64" t="n">
-        <v>196.09</v>
+        <v>-173.36</v>
       </c>
       <c r="E64" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F64" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G64" t="n">
-        <v>65.17</v>
+        <v>279.59</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1632</v>
+      </c>
+      <c r="L64" t="n">
+        <v>115</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.858</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:11.355</t>
+          <t>2026-05-29 09:40:25.657</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421933303</v>
+        <v>1780022423991</v>
       </c>
       <c r="C65" t="n">
-        <v>86555</v>
+        <v>86458</v>
       </c>
       <c r="D65" t="n">
-        <v>384.29</v>
+        <v>286.31</v>
       </c>
       <c r="E65" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F65" t="n">
-        <v>725</v>
+        <v>1379</v>
       </c>
       <c r="G65" t="n">
-        <v>65.17</v>
+        <v>279.59</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1665</v>
+      </c>
+      <c r="L65" t="n">
+        <v>116</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.671</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:11.355</t>
+          <t>2026-05-29 09:40:25.657</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421933505</v>
+        <v>1780022424191</v>
       </c>
       <c r="C66" t="n">
-        <v>86827</v>
+        <v>86535</v>
       </c>
       <c r="D66" t="n">
-        <v>637.0700000000001</v>
+        <v>348.99</v>
       </c>
       <c r="E66" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F66" t="n">
-        <v>685</v>
+        <v>1379</v>
       </c>
       <c r="G66" t="n">
-        <v>59.6</v>
+        <v>279.59</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L66" t="n">
+        <v>109</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.463</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:11.817</t>
+          <t>2026-05-29 09:40:25.658</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421933706</v>
+        <v>1780022424391</v>
       </c>
       <c r="C67" t="n">
-        <v>86198</v>
+        <v>86207</v>
       </c>
       <c r="D67" t="n">
-        <v>-23.78</v>
+        <v>3.54</v>
       </c>
       <c r="E67" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F67" t="n">
-        <v>685</v>
+        <v>1379</v>
       </c>
       <c r="G67" t="n">
-        <v>59.6</v>
+        <v>279.59</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1266</v>
+      </c>
+      <c r="L67" t="n">
+        <v>109</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.517</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:11.824</t>
+          <t>2026-05-29 09:40:25.659</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421933907</v>
+        <v>1780022424591</v>
       </c>
       <c r="C68" t="n">
-        <v>86395</v>
+        <v>86468</v>
       </c>
       <c r="D68" t="n">
-        <v>174.41</v>
+        <v>264.37</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F68" t="n">
-        <v>685</v>
+        <v>1379</v>
       </c>
       <c r="G68" t="n">
-        <v>59.6</v>
+        <v>279.59</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L68" t="n">
+        <v>114</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:12.179</t>
+          <t>2026-05-29 09:40:26.203</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421934109</v>
+        <v>1780022424791</v>
       </c>
       <c r="C69" t="n">
-        <v>86699</v>
+        <v>87052</v>
       </c>
       <c r="D69" t="n">
-        <v>469.69</v>
+        <v>835.15</v>
       </c>
       <c r="E69" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F69" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G69" t="n">
-        <v>59.6</v>
+        <v>279.59</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L69" t="n">
+        <v>115</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.034</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:12.180</t>
+          <t>2026-05-29 09:40:26.204</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421934310</v>
+        <v>1780022424991</v>
       </c>
       <c r="C70" t="n">
-        <v>86134</v>
+        <v>87543</v>
       </c>
       <c r="D70" t="n">
-        <v>-118.8</v>
+        <v>1284.39</v>
       </c>
       <c r="E70" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F70" t="n">
-        <v>705</v>
+        <v>17271</v>
       </c>
       <c r="G70" t="n">
-        <v>54.59</v>
+        <v>279.59</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L70" t="n">
+        <v>127</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.024</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:12.566</t>
+          <t>2026-05-29 09:40:26.206</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421934512</v>
+        <v>1780022425191</v>
       </c>
       <c r="C71" t="n">
-        <v>86300</v>
+        <v>86444</v>
       </c>
       <c r="D71" t="n">
-        <v>53.14</v>
+        <v>121.17</v>
       </c>
       <c r="E71" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F71" t="n">
-        <v>705</v>
+        <v>17271</v>
       </c>
       <c r="G71" t="n">
-        <v>54.59</v>
+        <v>279.59</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L71" t="n">
+        <v>121</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.672</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:12.567</t>
+          <t>2026-05-29 09:40:26.531</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421934713</v>
+        <v>1780022425410</v>
       </c>
       <c r="C72" t="n">
-        <v>86545</v>
+        <v>85772</v>
       </c>
       <c r="D72" t="n">
-        <v>295.49</v>
+        <v>-556.89</v>
       </c>
       <c r="E72" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F72" t="n">
-        <v>705</v>
+        <v>17271</v>
       </c>
       <c r="G72" t="n">
-        <v>54.59</v>
+        <v>279.59</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L72" t="n">
+        <v>124</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.579</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.016</t>
+          <t>2026-05-29 09:40:26.532</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421934914</v>
+        <v>1780022425610</v>
       </c>
       <c r="C73" t="n">
-        <v>86806</v>
+        <v>84877</v>
       </c>
       <c r="D73" t="n">
-        <v>541.71</v>
+        <v>-1424.04</v>
       </c>
       <c r="E73" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F73" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G73" t="n">
-        <v>39.14</v>
+        <v>279.59</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K73" t="n">
+        <v>921</v>
+      </c>
+      <c r="L73" t="n">
+        <v>114</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.643</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.017</t>
+          <t>2026-05-29 09:40:27.063</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421935116</v>
+        <v>1780022425810</v>
       </c>
       <c r="C74" t="n">
-        <v>86012</v>
+        <v>84639</v>
       </c>
       <c r="D74" t="n">
-        <v>-279.37</v>
+        <v>-1590.84</v>
       </c>
       <c r="E74" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F74" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G74" t="n">
-        <v>39.14</v>
+        <v>279.59</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L74" t="n">
+        <v>120</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.571</t>
+          <t>2026-05-29 09:40:27.064</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421935317</v>
+        <v>1780022426010</v>
       </c>
       <c r="C75" t="n">
-        <v>86337</v>
+        <v>87491</v>
       </c>
       <c r="D75" t="n">
-        <v>59.6</v>
+        <v>1340.7</v>
       </c>
       <c r="E75" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F75" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G75" t="n">
-        <v>39.14</v>
+        <v>279.59</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L75" t="n">
+        <v>117</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.963</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.572</t>
+          <t>2026-05-29 09:40:27.291</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421935519</v>
+        <v>1780022426210</v>
       </c>
       <c r="C76" t="n">
-        <v>86615</v>
+        <v>84666</v>
       </c>
       <c r="D76" t="n">
-        <v>334.62</v>
+        <v>-1551.33</v>
       </c>
       <c r="E76" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F76" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G76" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L76" t="n">
+        <v>126</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.911</t>
+          <t>2026-05-29 09:40:27.293</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421935720</v>
+        <v>1780022426410</v>
       </c>
       <c r="C77" t="n">
-        <v>86340</v>
+        <v>84921</v>
       </c>
       <c r="D77" t="n">
-        <v>42.88</v>
+        <v>-1218.77</v>
       </c>
       <c r="E77" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F77" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G77" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K77" t="n">
+        <v>882</v>
+      </c>
+      <c r="L77" t="n">
+        <v>109</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.482</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.912</t>
+          <t>2026-05-29 09:40:27.791</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421935921</v>
+        <v>1780022426610</v>
       </c>
       <c r="C78" t="n">
-        <v>86218</v>
+        <v>84935</v>
       </c>
       <c r="D78" t="n">
-        <v>-81.26000000000001</v>
+        <v>-1143.83</v>
       </c>
       <c r="E78" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F78" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G78" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L78" t="n">
+        <v>132</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.042</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:13.914</t>
+          <t>2026-05-29 09:40:27.792</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421936123</v>
+        <v>1780022426810</v>
       </c>
       <c r="C79" t="n">
-        <v>86426</v>
+        <v>85216</v>
       </c>
       <c r="D79" t="n">
-        <v>130.8</v>
+        <v>-805.64</v>
       </c>
       <c r="E79" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F79" t="n">
-        <v>685</v>
+        <v>17271</v>
       </c>
       <c r="G79" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K79" t="n">
+        <v>981</v>
+      </c>
+      <c r="L79" t="n">
+        <v>117</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:14.213</t>
+          <t>2026-05-29 09:40:28.105</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421936324</v>
+        <v>1780022427029</v>
       </c>
       <c r="C80" t="n">
-        <v>86679</v>
+        <v>85381</v>
       </c>
       <c r="D80" t="n">
-        <v>377.26</v>
+        <v>-600.36</v>
       </c>
       <c r="E80" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F80" t="n">
-        <v>745</v>
+        <v>17271</v>
       </c>
       <c r="G80" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L80" t="n">
+        <v>119</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.717</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:14.649</t>
+          <t>2026-05-29 09:40:28.106</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421936526</v>
+        <v>1780022427229</v>
       </c>
       <c r="C81" t="n">
-        <v>86018</v>
+        <v>85331</v>
       </c>
       <c r="D81" t="n">
-        <v>-302.6</v>
+        <v>-620.34</v>
       </c>
       <c r="E81" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F81" t="n">
-        <v>745</v>
+        <v>17271</v>
       </c>
       <c r="G81" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K81" t="n">
+        <v>876</v>
+      </c>
+      <c r="L81" t="n">
+        <v>110</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.866</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:14.691</t>
+          <t>2026-05-29 09:40:28.409</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421936727</v>
+        <v>1780022427429</v>
       </c>
       <c r="C82" t="n">
-        <v>86317</v>
+        <v>85385</v>
       </c>
       <c r="D82" t="n">
-        <v>11.53</v>
+        <v>-535.3200000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F82" t="n">
-        <v>745</v>
+        <v>17271</v>
       </c>
       <c r="G82" t="n">
-        <v>41.09</v>
+        <v>279.59</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>978</v>
+      </c>
+      <c r="L82" t="n">
+        <v>126</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.911</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:15.048</t>
+          <t>2026-05-29 09:40:28.411</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421936928</v>
+        <v>1780022427629</v>
       </c>
       <c r="C83" t="n">
-        <v>86603</v>
+        <v>84010</v>
       </c>
       <c r="D83" t="n">
-        <v>296.95</v>
+        <v>-1883.55</v>
       </c>
       <c r="E83" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F83" t="n">
-        <v>664</v>
+        <v>2758</v>
       </c>
       <c r="G83" t="n">
-        <v>43.62</v>
+        <v>279.59</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K83" t="n">
+        <v>781</v>
+      </c>
+      <c r="L83" t="n">
+        <v>113</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.374</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:15.058</t>
+          <t>2026-05-29 09:40:28.932</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421937130</v>
+        <v>1780022427829</v>
       </c>
       <c r="C84" t="n">
-        <v>86262</v>
+        <v>83508</v>
       </c>
       <c r="D84" t="n">
-        <v>-58.89</v>
+        <v>-2291.38</v>
       </c>
       <c r="E84" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F84" t="n">
-        <v>664</v>
+        <v>2758</v>
       </c>
       <c r="G84" t="n">
-        <v>43.62</v>
+        <v>279.59</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L84" t="n">
+        <v>121</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.644</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:15.451</t>
+          <t>2026-05-29 09:40:28.934</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421937331</v>
+        <v>1780022428029</v>
       </c>
       <c r="C85" t="n">
-        <v>86240</v>
+        <v>83947</v>
       </c>
       <c r="D85" t="n">
-        <v>-77.95</v>
+        <v>-1737.81</v>
       </c>
       <c r="E85" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F85" t="n">
-        <v>664</v>
+        <v>2758</v>
       </c>
       <c r="G85" t="n">
-        <v>43.62</v>
+        <v>279.59</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>903</v>
+      </c>
+      <c r="L85" t="n">
+        <v>108</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.873</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:15.452</t>
+          <t>2026-05-29 09:40:29.343</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421937533</v>
+        <v>1780022428229</v>
       </c>
       <c r="C86" t="n">
-        <v>86510</v>
+        <v>84142</v>
       </c>
       <c r="D86" t="n">
-        <v>195.95</v>
+        <v>-1455.92</v>
       </c>
       <c r="E86" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F86" t="n">
-        <v>664</v>
+        <v>2758</v>
       </c>
       <c r="G86" t="n">
-        <v>43.62</v>
+        <v>279.59</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L86" t="n">
+        <v>120</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.834</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.085</t>
+          <t>2026-05-29 09:40:29.348</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421937734</v>
+        <v>1780022428429</v>
       </c>
       <c r="C87" t="n">
-        <v>86873</v>
+        <v>84231</v>
       </c>
       <c r="D87" t="n">
-        <v>549.15</v>
+        <v>-1294.12</v>
       </c>
       <c r="E87" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F87" t="n">
-        <v>726</v>
+        <v>2758</v>
       </c>
       <c r="G87" t="n">
-        <v>31.56</v>
+        <v>279.59</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K87" t="n">
+        <v>918</v>
+      </c>
+      <c r="L87" t="n">
+        <v>119</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.078</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.086</t>
+          <t>2026-05-29 09:40:29.731</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421937936</v>
+        <v>1780022428629</v>
       </c>
       <c r="C88" t="n">
-        <v>86155</v>
+        <v>84359</v>
       </c>
       <c r="D88" t="n">
-        <v>-196.31</v>
+        <v>-1101.42</v>
       </c>
       <c r="E88" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F88" t="n">
-        <v>726</v>
+        <v>2758</v>
       </c>
       <c r="G88" t="n">
-        <v>31.56</v>
+        <v>279.59</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L88" t="n">
+        <v>111</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.392</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.087</t>
+          <t>2026-05-29 09:40:29.732</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421938137</v>
+        <v>1780022428829</v>
       </c>
       <c r="C89" t="n">
-        <v>86421</v>
+        <v>83651</v>
       </c>
       <c r="D89" t="n">
-        <v>79.51000000000001</v>
+        <v>-1754.35</v>
       </c>
       <c r="E89" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F89" t="n">
-        <v>726</v>
+        <v>2758</v>
       </c>
       <c r="G89" t="n">
-        <v>31.56</v>
+        <v>279.59</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K89" t="n">
+        <v>902</v>
+      </c>
+      <c r="L89" t="n">
+        <v>107</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.983</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.094</t>
+          <t>2026-05-29 09:40:30.082</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421938338</v>
+        <v>1780022429048</v>
       </c>
       <c r="C90" t="n">
-        <v>86708</v>
+        <v>83176</v>
       </c>
       <c r="D90" t="n">
-        <v>362.53</v>
+        <v>-2141.63</v>
       </c>
       <c r="E90" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F90" t="n">
-        <v>726</v>
+        <v>2758</v>
       </c>
       <c r="G90" t="n">
-        <v>31.56</v>
+        <v>279.59</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L90" t="n">
+        <v>116</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.481</t>
+          <t>2026-05-29 09:40:30.083</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421938540</v>
+        <v>1780022429248</v>
       </c>
       <c r="C91" t="n">
-        <v>86994</v>
+        <v>83326</v>
       </c>
       <c r="D91" t="n">
-        <v>630.41</v>
+        <v>-1884.55</v>
       </c>
       <c r="E91" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F91" t="n">
-        <v>745</v>
+        <v>2758</v>
       </c>
       <c r="G91" t="n">
-        <v>33.14</v>
+        <v>279.59</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K91" t="n">
+        <v>834</v>
+      </c>
+      <c r="L91" t="n">
+        <v>110</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.059</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.515</t>
+          <t>2026-05-29 09:40:30.678</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421938741</v>
+        <v>1780022429448</v>
       </c>
       <c r="C92" t="n">
-        <v>86210</v>
+        <v>83173</v>
       </c>
       <c r="D92" t="n">
-        <v>-185.11</v>
+        <v>-1943.32</v>
       </c>
       <c r="E92" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F92" t="n">
-        <v>745</v>
+        <v>2758</v>
       </c>
       <c r="G92" t="n">
-        <v>33.14</v>
+        <v>279.59</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L92" t="n">
+        <v>121</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.666</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.888</t>
+          <t>2026-05-29 09:40:30.686</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421938943</v>
+        <v>1780022429648</v>
       </c>
       <c r="C93" t="n">
-        <v>86727</v>
+        <v>83294</v>
       </c>
       <c r="D93" t="n">
-        <v>341.14</v>
+        <v>-1725.15</v>
       </c>
       <c r="E93" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F93" t="n">
-        <v>745</v>
+        <v>2758</v>
       </c>
       <c r="G93" t="n">
-        <v>33.14</v>
+        <v>279.59</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L93" t="n">
+        <v>111</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:16.898</t>
+          <t>2026-05-29 09:40:31.119</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421939144</v>
+        <v>1780022429848</v>
       </c>
       <c r="C94" t="n">
-        <v>87067</v>
+        <v>83379</v>
       </c>
       <c r="D94" t="n">
-        <v>664.08</v>
+        <v>-1553.9</v>
       </c>
       <c r="E94" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F94" t="n">
-        <v>684</v>
+        <v>2758</v>
       </c>
       <c r="G94" t="n">
-        <v>28.6</v>
+        <v>279.59</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1269</v>
+      </c>
+      <c r="L94" t="n">
+        <v>123</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.542</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:17.693</t>
+          <t>2026-05-29 09:40:31.134</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421939345</v>
+        <v>1780022430048</v>
       </c>
       <c r="C95" t="n">
-        <v>86681</v>
+        <v>83562</v>
       </c>
       <c r="D95" t="n">
-        <v>244.88</v>
+        <v>-1293.2</v>
       </c>
       <c r="E95" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F95" t="n">
-        <v>684</v>
+        <v>2758</v>
       </c>
       <c r="G95" t="n">
-        <v>28.6</v>
+        <v>279.59</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L95" t="n">
+        <v>121</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.155</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:17.694</t>
+          <t>2026-05-29 09:40:32.121</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421939547</v>
+        <v>1780022430248</v>
       </c>
       <c r="C96" t="n">
-        <v>86668</v>
+        <v>83726</v>
       </c>
       <c r="D96" t="n">
-        <v>219.64</v>
+        <v>-1064.54</v>
       </c>
       <c r="E96" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F96" t="n">
-        <v>684</v>
+        <v>2758</v>
       </c>
       <c r="G96" t="n">
-        <v>28.6</v>
+        <v>279.59</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1873</v>
+      </c>
+      <c r="L96" t="n">
+        <v>110</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.444</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:17.695</t>
+          <t>2026-05-29 09:40:32.122</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421939748</v>
+        <v>1780022430448</v>
       </c>
       <c r="C97" t="n">
-        <v>86942</v>
+        <v>83294</v>
       </c>
       <c r="D97" t="n">
-        <v>482.65</v>
+        <v>-1443.31</v>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F97" t="n">
-        <v>684</v>
+        <v>2758</v>
       </c>
       <c r="G97" t="n">
-        <v>28.6</v>
+        <v>279.59</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1674</v>
+      </c>
+      <c r="L97" t="n">
+        <v>112</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.459</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:17.701</t>
+          <t>2026-05-29 09:40:32.436</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421939949</v>
+        <v>1780022430649</v>
       </c>
       <c r="C98" t="n">
-        <v>87271</v>
+        <v>83535</v>
       </c>
       <c r="D98" t="n">
-        <v>787.52</v>
+        <v>-1130.15</v>
       </c>
       <c r="E98" t="n">
         <v>81</v>
       </c>
       <c r="F98" t="n">
-        <v>766</v>
+        <v>2758</v>
       </c>
       <c r="G98" t="n">
-        <v>34.2</v>
+        <v>279.59</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L98" t="n">
+        <v>106</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.415</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:18.125</t>
+          <t>2026-05-29 09:40:32.438</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421940151</v>
+        <v>1780022430867</v>
       </c>
       <c r="C99" t="n">
-        <v>86426</v>
+        <v>84532</v>
       </c>
       <c r="D99" t="n">
-        <v>-96.84999999999999</v>
+        <v>-76.64</v>
       </c>
       <c r="E99" t="n">
         <v>81</v>
       </c>
       <c r="F99" t="n">
-        <v>766</v>
+        <v>3378</v>
       </c>
       <c r="G99" t="n">
-        <v>34.2</v>
+        <v>279.59</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1570</v>
+      </c>
+      <c r="L99" t="n">
+        <v>110</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.127</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:18.131</t>
+          <t>2026-05-29 09:40:32.440</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421940352</v>
+        <v>1780022431067</v>
       </c>
       <c r="C100" t="n">
-        <v>86763</v>
+        <v>85012</v>
       </c>
       <c r="D100" t="n">
-        <v>244.99</v>
+        <v>407.19</v>
       </c>
       <c r="E100" t="n">
         <v>81</v>
       </c>
       <c r="F100" t="n">
-        <v>766</v>
+        <v>3378</v>
       </c>
       <c r="G100" t="n">
-        <v>34.2</v>
+        <v>279.59</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1371</v>
+      </c>
+      <c r="L100" t="n">
+        <v>107</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:18.524</t>
+          <t>2026-05-29 09:40:32.443</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421940554</v>
+        <v>1780022431267</v>
       </c>
       <c r="C101" t="n">
-        <v>87099</v>
+        <v>85461</v>
       </c>
       <c r="D101" t="n">
-        <v>568.74</v>
+        <v>835.83</v>
       </c>
       <c r="E101" t="n">
         <v>81</v>
       </c>
       <c r="F101" t="n">
-        <v>766</v>
+        <v>3378</v>
       </c>
       <c r="G101" t="n">
-        <v>34.2</v>
+        <v>279.59</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L101" t="n">
+        <v>106</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.962</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:18.525</t>
+          <t>2026-05-29 09:40:34.086</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421940755</v>
+        <v>1780022431467</v>
       </c>
       <c r="C102" t="n">
-        <v>86793</v>
+        <v>86588</v>
       </c>
       <c r="D102" t="n">
-        <v>234.3</v>
+        <v>1921.04</v>
       </c>
       <c r="E102" t="n">
         <v>81</v>
       </c>
       <c r="F102" t="n">
-        <v>725</v>
+        <v>3378</v>
       </c>
       <c r="G102" t="n">
-        <v>33.41</v>
+        <v>279.59</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2618</v>
+      </c>
+      <c r="L102" t="n">
+        <v>112</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.124</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.405</t>
+          <t>2026-05-29 09:40:34.087</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421940956</v>
+        <v>1780022431667</v>
       </c>
       <c r="C103" t="n">
-        <v>86534</v>
+        <v>87371</v>
       </c>
       <c r="D103" t="n">
-        <v>-36.41</v>
+        <v>2607.99</v>
       </c>
       <c r="E103" t="n">
         <v>81</v>
       </c>
       <c r="F103" t="n">
-        <v>725</v>
+        <v>3378</v>
       </c>
       <c r="G103" t="n">
-        <v>33.41</v>
+        <v>279.59</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2419</v>
+      </c>
+      <c r="L103" t="n">
+        <v>115</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.406</t>
+          <t>2026-05-29 09:40:34.088</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421941158</v>
+        <v>1780022431867</v>
       </c>
       <c r="C104" t="n">
-        <v>86736</v>
+        <v>87639</v>
       </c>
       <c r="D104" t="n">
-        <v>167.41</v>
+        <v>2745.59</v>
       </c>
       <c r="E104" t="n">
         <v>81</v>
       </c>
       <c r="F104" t="n">
-        <v>725</v>
+        <v>3378</v>
       </c>
       <c r="G104" t="n">
-        <v>33.41</v>
+        <v>279.59</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2220</v>
+      </c>
+      <c r="L104" t="n">
+        <v>119</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.539</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.407</t>
+          <t>2026-05-29 09:40:34.089</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421941359</v>
+        <v>1780022432067</v>
       </c>
       <c r="C105" t="n">
-        <v>87044</v>
+        <v>87462</v>
       </c>
       <c r="D105" t="n">
-        <v>467.04</v>
+        <v>2431.31</v>
       </c>
       <c r="E105" t="n">
         <v>81</v>
       </c>
       <c r="F105" t="n">
-        <v>765</v>
+        <v>3378</v>
       </c>
       <c r="G105" t="n">
-        <v>37</v>
+        <v>279.59</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L105" t="n">
+        <v>116</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.407</t>
+          <t>2026-05-29 09:40:34.089</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421941561</v>
+        <v>1780022432267</v>
       </c>
       <c r="C106" t="n">
-        <v>86248</v>
+        <v>85663</v>
       </c>
       <c r="D106" t="n">
-        <v>-352.31</v>
+        <v>510.74</v>
       </c>
       <c r="E106" t="n">
         <v>81</v>
       </c>
       <c r="F106" t="n">
-        <v>765</v>
+        <v>3378</v>
       </c>
       <c r="G106" t="n">
-        <v>37</v>
+        <v>279.59</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1822</v>
+      </c>
+      <c r="L106" t="n">
+        <v>117</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.771</t>
+          <t>2026-05-29 09:40:34.090</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421941762</v>
+        <v>1780022432467</v>
       </c>
       <c r="C107" t="n">
-        <v>86684</v>
+        <v>84934</v>
       </c>
       <c r="D107" t="n">
-        <v>101.3</v>
+        <v>-243.79</v>
       </c>
       <c r="E107" t="n">
         <v>81</v>
       </c>
       <c r="F107" t="n">
-        <v>765</v>
+        <v>3378</v>
       </c>
       <c r="G107" t="n">
-        <v>37</v>
+        <v>279.59</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1622</v>
+      </c>
+      <c r="L107" t="n">
+        <v>105</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.486</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:19.772</t>
+          <t>2026-05-29 09:40:34.171</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421941963</v>
+        <v>1780022432686</v>
       </c>
       <c r="C108" t="n">
-        <v>87056</v>
+        <v>84132</v>
       </c>
       <c r="D108" t="n">
-        <v>468.24</v>
+        <v>-1033.6</v>
       </c>
       <c r="E108" t="n">
         <v>81</v>
       </c>
       <c r="F108" t="n">
-        <v>765</v>
+        <v>3378</v>
       </c>
       <c r="G108" t="n">
-        <v>37</v>
+        <v>279.59</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L108" t="n">
+        <v>119</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.971</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:20.369</t>
+          <t>2026-05-29 09:40:34.305</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421942165</v>
+        <v>1780022432886</v>
       </c>
       <c r="C109" t="n">
-        <v>87250</v>
+        <v>84094</v>
       </c>
       <c r="D109" t="n">
-        <v>638.8200000000001</v>
+        <v>-1019.92</v>
       </c>
       <c r="E109" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F109" t="n">
-        <v>645</v>
+        <v>3378</v>
       </c>
       <c r="G109" t="n">
-        <v>42.8</v>
+        <v>279.59</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L109" t="n">
+        <v>115</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:20.370</t>
+          <t>2026-05-29 09:40:34.421</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421942366</v>
+        <v>1780022433086</v>
       </c>
       <c r="C110" t="n">
-        <v>86481</v>
+        <v>84497</v>
       </c>
       <c r="D110" t="n">
-        <v>-162.12</v>
+        <v>-565.9299999999999</v>
       </c>
       <c r="E110" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F110" t="n">
-        <v>645</v>
+        <v>3378</v>
       </c>
       <c r="G110" t="n">
-        <v>42.8</v>
+        <v>279.59</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1333</v>
+      </c>
+      <c r="L110" t="n">
+        <v>121</v>
+      </c>
+      <c r="M110" t="n">
+        <v>2.022</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:20.371</t>
+          <t>2026-05-29 09:40:34.565</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421942568</v>
+        <v>1780022433286</v>
       </c>
       <c r="C111" t="n">
-        <v>86720</v>
+        <v>84899</v>
       </c>
       <c r="D111" t="n">
-        <v>84.98999999999999</v>
+        <v>-135.63</v>
       </c>
       <c r="E111" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F111" t="n">
-        <v>645</v>
+        <v>3378</v>
       </c>
       <c r="G111" t="n">
-        <v>42.8</v>
+        <v>279.59</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L111" t="n">
+        <v>119</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.328</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:20.803</t>
+          <t>2026-05-29 09:40:34.566</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421942769</v>
+        <v>1780022433486</v>
       </c>
       <c r="C112" t="n">
-        <v>86984</v>
+        <v>84510</v>
       </c>
       <c r="D112" t="n">
-        <v>344.74</v>
+        <v>-517.85</v>
       </c>
       <c r="E112" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F112" t="n">
-        <v>645</v>
+        <v>3378</v>
       </c>
       <c r="G112" t="n">
-        <v>42.8</v>
+        <v>279.59</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L112" t="n">
+        <v>109</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.139</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:34.787</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022433687</v>
+      </c>
+      <c r="C113" t="n">
+        <v>83951</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-1050.96</v>
+      </c>
+      <c r="E113" t="n">
+        <v>81</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G113" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1099</v>
+      </c>
+      <c r="L113" t="n">
+        <v>107</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.267</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:34.789</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022433886</v>
+      </c>
+      <c r="C114" t="n">
+        <v>83551</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-1398.41</v>
+      </c>
+      <c r="E114" t="n">
+        <v>81</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G114" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K114" t="n">
+        <v>902</v>
+      </c>
+      <c r="L114" t="n">
+        <v>122</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.242</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:35.238</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022434087</v>
+      </c>
+      <c r="C115" t="n">
+        <v>82929</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-1950.49</v>
+      </c>
+      <c r="E115" t="n">
+        <v>81</v>
+      </c>
+      <c r="F115" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G115" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L115" t="n">
+        <v>109</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:35.239</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022434286</v>
+      </c>
+      <c r="C116" t="n">
+        <v>83264</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-1517.96</v>
+      </c>
+      <c r="E116" t="n">
+        <v>81</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G116" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K116" t="n">
+        <v>952</v>
+      </c>
+      <c r="L116" t="n">
+        <v>117</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:35.636</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022434505</v>
+      </c>
+      <c r="C117" t="n">
+        <v>83739</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-967.0700000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>81</v>
+      </c>
+      <c r="F117" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G117" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L117" t="n">
+        <v>116</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:35.637</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022434705</v>
+      </c>
+      <c r="C118" t="n">
+        <v>83405</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-1252.71</v>
+      </c>
+      <c r="E118" t="n">
+        <v>81</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G118" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K118" t="n">
+        <v>931</v>
+      </c>
+      <c r="L118" t="n">
+        <v>115</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.034</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022434905</v>
+      </c>
+      <c r="C119" t="n">
+        <v>82774</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-1821.08</v>
+      </c>
+      <c r="E119" t="n">
+        <v>81</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G119" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1128</v>
+      </c>
+      <c r="L119" t="n">
+        <v>109</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.035</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022435105</v>
+      </c>
+      <c r="C120" t="n">
+        <v>82269</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-2235.02</v>
+      </c>
+      <c r="E120" t="n">
+        <v>81</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G120" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K120" t="n">
+        <v>930</v>
+      </c>
+      <c r="L120" t="n">
+        <v>141</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.613</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022435306</v>
+      </c>
+      <c r="C121" t="n">
+        <v>82921</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-1471.27</v>
+      </c>
+      <c r="E121" t="n">
+        <v>81</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G121" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L121" t="n">
+        <v>105</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.174</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.614</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022435505</v>
+      </c>
+      <c r="C122" t="n">
+        <v>83274</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-1044.71</v>
+      </c>
+      <c r="E122" t="n">
+        <v>81</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G122" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L122" t="n">
+        <v>115</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.615</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022435706</v>
+      </c>
+      <c r="C123" t="n">
+        <v>83666</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-600.47</v>
+      </c>
+      <c r="E123" t="n">
+        <v>81</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G123" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="J123" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="K123" t="n">
+        <v>909</v>
+      </c>
+      <c r="L123" t="n">
+        <v>106</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.549</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.988</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022435905</v>
+      </c>
+      <c r="C124" t="n">
+        <v>83125</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-1111.45</v>
+      </c>
+      <c r="E124" t="n">
+        <v>81</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G124" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1081</v>
+      </c>
+      <c r="L124" t="n">
+        <v>108</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.252</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:36.990</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022436106</v>
+      </c>
+      <c r="C125" t="n">
+        <v>83100</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1080.88</v>
+      </c>
+      <c r="E125" t="n">
+        <v>81</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G125" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K125" t="n">
+        <v>882</v>
+      </c>
+      <c r="L125" t="n">
+        <v>115</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:37.980</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022436324</v>
+      </c>
+      <c r="C126" t="n">
+        <v>83832</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-294.83</v>
+      </c>
+      <c r="E126" t="n">
+        <v>81</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G126" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1655</v>
+      </c>
+      <c r="L126" t="n">
+        <v>115</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.967</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:37.990</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022436524</v>
+      </c>
+      <c r="C127" t="n">
+        <v>83649</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-463.09</v>
+      </c>
+      <c r="E127" t="n">
+        <v>81</v>
+      </c>
+      <c r="F127" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G127" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1465</v>
+      </c>
+      <c r="L127" t="n">
+        <v>125</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.987</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:37.997</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022436724</v>
+      </c>
+      <c r="C128" t="n">
+        <v>83479</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-609.9400000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>81</v>
+      </c>
+      <c r="F128" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G128" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1272</v>
+      </c>
+      <c r="L128" t="n">
+        <v>104</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.697</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:38.029</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022436925</v>
+      </c>
+      <c r="C129" t="n">
+        <v>82911</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-1147.44</v>
+      </c>
+      <c r="E129" t="n">
+        <v>81</v>
+      </c>
+      <c r="F129" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G129" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1103</v>
+      </c>
+      <c r="L129" t="n">
+        <v>107</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:38.571</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022437124</v>
+      </c>
+      <c r="C130" t="n">
+        <v>83392</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-609.0700000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>81</v>
+      </c>
+      <c r="F130" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G130" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1446</v>
+      </c>
+      <c r="L130" t="n">
+        <v>100</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.324</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:38.572</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022437324</v>
+      </c>
+      <c r="C131" t="n">
+        <v>83529</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-441.61</v>
+      </c>
+      <c r="E131" t="n">
+        <v>81</v>
+      </c>
+      <c r="F131" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G131" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1248</v>
+      </c>
+      <c r="L131" t="n">
+        <v>117</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.638</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:38.573</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022437524</v>
+      </c>
+      <c r="C132" t="n">
+        <v>84167</v>
+      </c>
+      <c r="D132" t="n">
+        <v>218.47</v>
+      </c>
+      <c r="E132" t="n">
+        <v>81</v>
+      </c>
+      <c r="F132" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G132" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L132" t="n">
+        <v>105</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:39.362</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022437724</v>
+      </c>
+      <c r="C133" t="n">
+        <v>84105</v>
+      </c>
+      <c r="D133" t="n">
+        <v>145.54</v>
+      </c>
+      <c r="E133" t="n">
+        <v>81</v>
+      </c>
+      <c r="F133" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G133" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1637</v>
+      </c>
+      <c r="L133" t="n">
+        <v>122</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.527</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:39.364</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022437943</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83386</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-580.73</v>
+      </c>
+      <c r="E134" t="n">
+        <v>81</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G134" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1420</v>
+      </c>
+      <c r="L134" t="n">
+        <v>122</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:39.365</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022438143</v>
+      </c>
+      <c r="C135" t="n">
+        <v>83830</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-107.7</v>
+      </c>
+      <c r="E135" t="n">
+        <v>81</v>
+      </c>
+      <c r="F135" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G135" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L135" t="n">
+        <v>105</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:40.100</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022438343</v>
+      </c>
+      <c r="C136" t="n">
+        <v>83069</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-863.3099999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>81</v>
+      </c>
+      <c r="F136" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G136" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1756</v>
+      </c>
+      <c r="L136" t="n">
+        <v>123</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:40.101</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022438543</v>
+      </c>
+      <c r="C137" t="n">
+        <v>84888</v>
+      </c>
+      <c r="D137" t="n">
+        <v>998.85</v>
+      </c>
+      <c r="E137" t="n">
+        <v>81</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5477</v>
+      </c>
+      <c r="G137" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1557</v>
+      </c>
+      <c r="L137" t="n">
+        <v>112</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:40.102</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022438743</v>
+      </c>
+      <c r="C138" t="n">
+        <v>84198</v>
+      </c>
+      <c r="D138" t="n">
+        <v>258.91</v>
+      </c>
+      <c r="E138" t="n">
+        <v>81</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2319</v>
+      </c>
+      <c r="G138" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L138" t="n">
+        <v>114</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:40.103</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022438943</v>
+      </c>
+      <c r="C139" t="n">
+        <v>86933</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2980.96</v>
+      </c>
+      <c r="E139" t="n">
+        <v>81</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2319</v>
+      </c>
+      <c r="G139" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L139" t="n">
+        <v>117</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.551</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:40:42.064</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022439143</v>
+      </c>
+      <c r="C140" t="n">
+        <v>86557</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2455.92</v>
+      </c>
+      <c r="E140" t="n">
+        <v>81</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2319</v>
+      </c>
+      <c r="G140" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2920</v>
+      </c>
+      <c r="L140" t="n">
+        <v>108</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.741</v>
       </c>
     </row>
   </sheetData>
